--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_DM GROUP MOLLET.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_DM GROUP MOLLET.xlsx
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>8.852500000000001</v>
+        <v>16.9388</v>
       </c>
       <c r="E2" t="n">
-        <v>10.198</v>
+        <v>16.7153</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3455</v>
+        <v>0.2237</v>
       </c>
       <c r="G2" t="n">
-        <v>10.0446</v>
+        <v>18.0829</v>
       </c>
       <c r="H2" t="n">
-        <v>4.038499999999999</v>
+        <v>12.6947</v>
       </c>
       <c r="I2" t="n">
-        <v>6.006</v>
+        <v>5.3883</v>
       </c>
       <c r="J2" t="n">
-        <v>11.1708</v>
+        <v>21.8176</v>
       </c>
       <c r="K2" t="n">
-        <v>5.6402</v>
+        <v>15.5745</v>
       </c>
       <c r="L2" t="n">
-        <v>5.5306</v>
+        <v>6.2431</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.1263</v>
+        <v>-3.7344</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.6017</v>
+        <v>-2.8798</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4753000000000001</v>
+        <v>-0.8547999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>2.6008</v>
+        <v>5.6474</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0006</v>
+        <v>-6.815799999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>4.6013</v>
+        <v>12.4632</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.0734</v>
+        <v>-6.5369</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.5716</v>
+        <v>-6.7307</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4981</v>
+        <v>0.1939</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.7194</v>
+        <v>-0.2546000000000004</v>
       </c>
       <c r="W2" t="n">
-        <v>3.5993</v>
+        <v>8.4442</v>
       </c>
       <c r="X2" t="n">
-        <v>-5.3186</v>
+        <v>-8.6988</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. VINALLONGA BLANCO</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5372</v>
+        <v>7.8929</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1443</v>
+        <v>5.2668</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3929</v>
+        <v>2.6261</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7197</v>
+        <v>2.2287</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3861000000000001</v>
+        <v>2.4601</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3337</v>
+        <v>-0.2314000000000003</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6506</v>
+        <v>6.021599999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4868</v>
+        <v>5.5835</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1637999999999999</v>
+        <v>0.4379999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9308000000000001</v>
+        <v>-3.7929</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1007</v>
+        <v>-3.1234</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1698999999999999</v>
+        <v>-0.6692</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6001000000000001</v>
+        <v>4.2842</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0003</v>
+        <v>-4.8685</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6004</v>
+        <v>9.152699999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4771</v>
+        <v>1.4652</v>
       </c>
       <c r="T3" t="n">
-        <v>1.494</v>
+        <v>0.5021</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9830999999999999</v>
+        <v>0.9631000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2598</v>
+        <v>-0.08519999999999972</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.6116</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2598</v>
+        <v>-3.6968</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2908</v>
+        <v>4.8369</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1024</v>
+        <v>7.6721</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3932</v>
+        <v>-2.8351</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8479</v>
+        <v>3.9001</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2022</v>
+        <v>4.7935</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3542</v>
+        <v>-0.8933999999999997</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8690000000000001</v>
+        <v>7.4032</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0272</v>
+        <v>7.215400000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8418</v>
+        <v>0.1878999999999997</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.717</v>
+        <v>-3.5032</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2294</v>
+        <v>-2.422</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4876</v>
+        <v>-1.0812</v>
       </c>
       <c r="P4" t="n">
-        <v>1.4004</v>
+        <v>3.5052</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0006</v>
+        <v>-7.7895</v>
       </c>
       <c r="R4" t="n">
-        <v>3.401</v>
+        <v>11.2948</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3099</v>
+        <v>-3.946899999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4292</v>
+        <v>-3.4388</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8806999999999999</v>
+        <v>-0.5080999999999998</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4284</v>
+        <v>1.3785</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5999</v>
+        <v>11.4967</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8285</v>
+        <v>-10.1186</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.543</v>
+        <v>3.9816</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5631</v>
+        <v>1.3326</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.0201</v>
+        <v>2.6491</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7799</v>
+        <v>4.6721</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0415</v>
+        <v>2.4228</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7385</v>
+        <v>2.2491</v>
       </c>
       <c r="J5" t="n">
-        <v>5.289800000000001</v>
+        <v>9.330400000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5283</v>
+        <v>5.714600000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>2.7615</v>
+        <v>3.6159</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5099</v>
+        <v>-4.6583</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4868</v>
+        <v>-3.2918</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0231</v>
+        <v>-1.3666</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2</v>
+        <v>0.9737</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.0012</v>
+        <v>-10.7105</v>
       </c>
       <c r="R5" t="n">
-        <v>3.8011</v>
+        <v>11.6841</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4827</v>
+        <v>-4.1267</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1845</v>
+        <v>-2.1716</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6673</v>
+        <v>-1.9551</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5194999999999999</v>
+        <v>2.4628</v>
       </c>
       <c r="W5" t="n">
-        <v>4.459000000000001</v>
+        <v>4.8844</v>
       </c>
       <c r="X5" t="n">
-        <v>-4.9786</v>
+        <v>-2.4216</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8166</v>
+        <v>2.6274</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7642</v>
+        <v>0.5496999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05249999999999999</v>
+        <v>2.0778</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1803</v>
+        <v>-1.4749</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2348</v>
+        <v>0.9734999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4152</v>
+        <v>-2.4483</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1251</v>
+        <v>3.0536</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1981</v>
+        <v>3.264</v>
       </c>
       <c r="L6" t="n">
-        <v>4.3232</v>
+        <v>-0.2103999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9447000000000001</v>
+        <v>-4.5284</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.03669999999999995</v>
+        <v>-2.2905</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.908</v>
+        <v>-2.2379</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.0005</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.0009</v>
+        <v>-6.2316</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0003</v>
+        <v>6.2315</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4514</v>
+        <v>4.5039</v>
       </c>
       <c r="T6" t="n">
-        <v>0.04010000000000002</v>
+        <v>3.4482</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4916</v>
+        <v>1.0558</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0883</v>
+        <v>-0.4016</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5999</v>
+        <v>0.2795</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4884000000000001</v>
+        <v>-0.6811</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5461</v>
+        <v>0.6158</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7616</v>
+        <v>0.6158</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2155</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6595</v>
+        <v>0.6158</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6556</v>
+        <v>0.6158</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9961</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4341</v>
+        <v>0.6158</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2397</v>
+        <v>0.6158</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8056</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2254</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4159</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1905</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.0009</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.8008</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8182</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5582</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5876</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>4.6384</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.0508</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3247</v>
+        <v>-1.4067</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4444</v>
+        <v>4.356</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1197</v>
+        <v>-5.762700000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4678</v>
+        <v>-4.6366</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6718000000000001</v>
+        <v>-3.9489</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7959</v>
+        <v>-0.6877</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8192</v>
+        <v>-0.8134</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7795</v>
+        <v>-1.8518</v>
       </c>
       <c r="L8" t="n">
-        <v>2.0397</v>
+        <v>1.0383</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3515</v>
+        <v>-3.8232</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1077</v>
+        <v>-2.0971</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2438</v>
+        <v>-1.7261</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.2004</v>
+        <v>0.7789000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.0009</v>
+        <v>-5.2578</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8005</v>
+        <v>6.0368</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9428000000000001</v>
+        <v>5.2361</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7735</v>
+        <v>3.7417</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1693</v>
+        <v>1.4947</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.7851</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3995</v>
+        <v>6.6859</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.3995</v>
+        <v>-9.471</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2999</v>
+        <v>-6.0524</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2999</v>
+        <v>-3.045</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-3.0074</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2999</v>
+        <v>-4.0703</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2999</v>
+        <v>-1.9421</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-2.1282</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2999</v>
+        <v>0.1026999999999996</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2999</v>
+        <v>1.4221</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.319299999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-4.1729</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-3.3641</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.8088000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.5579</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-9.9315</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>11.4895</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-3.3294</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.8952</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-2.4343</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.2106</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>7.678900000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-7.8896</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5112000000000001</v>
+        <v>-6.4595</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07969999999999999</v>
+        <v>-1.588</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5908</v>
+        <v>-4.8715</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7754</v>
+        <v>-1.302200000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2712</v>
+        <v>-1.1795</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5041</v>
+        <v>-0.1226999999999998</v>
       </c>
       <c r="J10" t="n">
-        <v>2.527</v>
+        <v>2.4423</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6434000000000001</v>
+        <v>-0.5899</v>
       </c>
       <c r="L10" t="n">
-        <v>1.8835</v>
+        <v>3.0324</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7516</v>
+        <v>-3.7444</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3722</v>
+        <v>-0.5892000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3794</v>
+        <v>-3.1552</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4001</v>
+        <v>-0.7789999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0003</v>
+        <v>-4.089399999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4004</v>
+        <v>3.3104</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8067</v>
+        <v>-2.6645</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7667999999999999</v>
+        <v>-1.1102</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0399</v>
+        <v>-1.5543</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.88</v>
+        <v>-1.7137</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6802</v>
+        <v>1.1695</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1998</v>
+        <v>-2.8833</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6347</v>
+        <v>-7.2506</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0834</v>
+        <v>-5.9526</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4487000000000001</v>
+        <v>-1.298</v>
       </c>
       <c r="G11" t="n">
-        <v>4.279500000000001</v>
+        <v>-0.8416000000000003</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5255</v>
+        <v>0.4278999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>1.754</v>
+        <v>-1.2694</v>
       </c>
       <c r="J11" t="n">
-        <v>6.1551</v>
+        <v>2.8528</v>
       </c>
       <c r="K11" t="n">
-        <v>4.0697</v>
+        <v>2.1632</v>
       </c>
       <c r="L11" t="n">
-        <v>2.0854</v>
+        <v>0.6895</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8756</v>
+        <v>-3.6941</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5443</v>
+        <v>-1.7353</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3313999999999999</v>
+        <v>-1.9589</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.601</v>
+        <v>-3.3107</v>
       </c>
       <c r="Q11" t="n">
-        <v>-8.0023</v>
+        <v>-8.178900000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>4.4013</v>
+        <v>4.868300000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.5809</v>
+        <v>-2.9953</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.6357</v>
+        <v>-1.7442</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9451999999999999</v>
+        <v>-1.2509</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2678</v>
+        <v>-0.1031000000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>2.3996</v>
+        <v>1.118</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1318</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7529</v>
+        <v>-9.164400000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>1.1018</v>
+        <v>-1.4471</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.8546</v>
+        <v>-7.7171</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.6186</v>
+        <v>0.1027</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.5338</v>
+        <v>-0.4760000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0848</v>
+        <v>0.5788000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.5937</v>
+        <v>4.5825</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.8471</v>
+        <v>2.5632</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7465999999999999</v>
+        <v>2.0193</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.0249</v>
+        <v>-4.4798</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.6867</v>
+        <v>-3.0393</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3382</v>
+        <v>-1.4405</v>
       </c>
       <c r="P12" t="n">
-        <v>1.2003</v>
+        <v>-1.9473</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.0009</v>
+        <v>-7.2053</v>
       </c>
       <c r="R12" t="n">
-        <v>4.2012</v>
+        <v>5.258</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7224</v>
+        <v>-2.4415</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8222</v>
+        <v>-1.8772</v>
       </c>
       <c r="U12" t="n">
-        <v>0.09969999999999996</v>
+        <v>-0.5643</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6122</v>
+        <v>-4.8782</v>
       </c>
       <c r="W12" t="n">
-        <v>6.5184</v>
+        <v>3.0526</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.130599999999999</v>
+        <v>-7.9308</v>
       </c>
     </row>
     <row r="13">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>17.312</v>
+        <v>6.559799999999994</v>
       </c>
       <c r="E13" t="n">
-        <v>23.1712</v>
+        <v>24.4756</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.858899999999999</v>
+        <v>-17.9151</v>
       </c>
       <c r="G13" t="n">
-        <v>20.4211</v>
+        <v>17.2767</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6081</v>
+        <v>16.8418</v>
       </c>
       <c r="I13" t="n">
-        <v>16.8129</v>
+        <v>0.4351000000000004</v>
       </c>
       <c r="J13" t="n">
-        <v>33.8787</v>
+        <v>57.40910000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>14.1901</v>
+        <v>41.67460000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>19.6885</v>
+        <v>15.7347</v>
       </c>
       <c r="M13" t="n">
-        <v>-13.4577</v>
+        <v>-40.1316</v>
       </c>
       <c r="N13" t="n">
-        <v>-10.5821</v>
+        <v>-24.8325</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.8758</v>
+        <v>-15.2992</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.0002</v>
+        <v>10.7103</v>
       </c>
       <c r="Q13" t="n">
-        <v>-30.0089</v>
+        <v>-71.07879999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>29.0083</v>
+        <v>81.78930000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4897</v>
+        <v>-14.836</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.232800000000001</v>
+        <v>-10.2759</v>
       </c>
       <c r="U13" t="n">
-        <v>3.742899999999999</v>
+        <v>-4.5595</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6187999999999997</v>
+        <v>-6.5908</v>
       </c>
       <c r="W13" t="n">
-        <v>24.5338</v>
+        <v>48.4213</v>
       </c>
       <c r="X13" t="n">
-        <v>-25.1526</v>
+        <v>-55.0127</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_DM GROUP MOLLET.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_DM GROUP MOLLET.xlsx
@@ -565,13 +565,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>16.9388</v>
+        <v>21.6562</v>
       </c>
       <c r="E2" t="n">
-        <v>16.7153</v>
+        <v>20.7125</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2237</v>
+        <v>0.9438000000000004</v>
       </c>
       <c r="G2" t="n">
         <v>18.0829</v>
@@ -610,13 +610,13 @@
         <v>12.4632</v>
       </c>
       <c r="S2" t="n">
-        <v>-6.5369</v>
+        <v>-1.8196</v>
       </c>
       <c r="T2" t="n">
-        <v>-6.7307</v>
+        <v>-2.7336</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1939</v>
+        <v>0.9139999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2546000000000004</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>7.8929</v>
+        <v>6.8009</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2668</v>
+        <v>8.9779</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6261</v>
+        <v>-2.1768</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2287</v>
+        <v>3.9001</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4601</v>
+        <v>4.7935</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2314000000000003</v>
+        <v>-0.8933999999999997</v>
       </c>
       <c r="J3" t="n">
-        <v>6.021599999999999</v>
+        <v>7.4032</v>
       </c>
       <c r="K3" t="n">
-        <v>5.5835</v>
+        <v>7.215400000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4379999999999999</v>
+        <v>0.1878999999999997</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.7929</v>
+        <v>-3.5032</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.1234</v>
+        <v>-2.422</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6692</v>
+        <v>-1.0812</v>
       </c>
       <c r="P3" t="n">
-        <v>4.2842</v>
+        <v>3.5052</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.8685</v>
+        <v>-7.7895</v>
       </c>
       <c r="R3" t="n">
-        <v>9.152699999999999</v>
+        <v>11.2948</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4652</v>
+        <v>-1.9826</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5021</v>
+        <v>-2.1327</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9631000000000001</v>
+        <v>0.1502000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.08519999999999972</v>
+        <v>1.3785</v>
       </c>
       <c r="W3" t="n">
-        <v>3.6116</v>
+        <v>11.4967</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.6968</v>
+        <v>-10.1186</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8369</v>
+        <v>6.327199999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>7.6721</v>
+        <v>2.2777</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.8351</v>
+        <v>4.0494</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9001</v>
+        <v>4.6721</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7935</v>
+        <v>2.4228</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8933999999999997</v>
+        <v>2.2491</v>
       </c>
       <c r="J4" t="n">
-        <v>7.4032</v>
+        <v>9.330400000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>7.215400000000001</v>
+        <v>5.714600000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1878999999999997</v>
+        <v>3.6159</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.5032</v>
+        <v>-4.6583</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.422</v>
+        <v>-3.2918</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0812</v>
+        <v>-1.3666</v>
       </c>
       <c r="P4" t="n">
-        <v>3.5052</v>
+        <v>0.9737</v>
       </c>
       <c r="Q4" t="n">
-        <v>-7.7895</v>
+        <v>-10.7105</v>
       </c>
       <c r="R4" t="n">
-        <v>11.2948</v>
+        <v>11.6841</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.946899999999999</v>
+        <v>-1.7812</v>
       </c>
       <c r="T4" t="n">
-        <v>-3.4388</v>
+        <v>-1.2264</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5080999999999998</v>
+        <v>-0.5548</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3785</v>
+        <v>2.4628</v>
       </c>
       <c r="W4" t="n">
-        <v>11.4967</v>
+        <v>4.8844</v>
       </c>
       <c r="X4" t="n">
-        <v>-10.1186</v>
+        <v>-2.4216</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>3.9816</v>
+        <v>6.2192</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3326</v>
+        <v>3.9951</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6491</v>
+        <v>2.2241</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6721</v>
+        <v>2.2287</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4228</v>
+        <v>2.4601</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2491</v>
+        <v>-0.2314000000000003</v>
       </c>
       <c r="J5" t="n">
-        <v>9.330400000000001</v>
+        <v>6.021599999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>5.714600000000001</v>
+        <v>5.5835</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6159</v>
+        <v>0.4379999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.6583</v>
+        <v>-3.7929</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.2918</v>
+        <v>-3.1234</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3666</v>
+        <v>-0.6692</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9737</v>
+        <v>4.2842</v>
       </c>
       <c r="Q5" t="n">
-        <v>-10.7105</v>
+        <v>-4.8685</v>
       </c>
       <c r="R5" t="n">
-        <v>11.6841</v>
+        <v>9.152699999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>-4.1267</v>
+        <v>-0.2085999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.1716</v>
+        <v>-0.7696000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.9551</v>
+        <v>0.5611</v>
       </c>
       <c r="V5" t="n">
-        <v>2.4628</v>
+        <v>-0.08519999999999972</v>
       </c>
       <c r="W5" t="n">
-        <v>4.8844</v>
+        <v>3.6116</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.4216</v>
+        <v>-3.6968</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. VINALLONGA BLANCO</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6274</v>
+        <v>0.6158</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5496999999999999</v>
+        <v>0.6158</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0778</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4749</v>
+        <v>0.6158</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9734999999999999</v>
+        <v>0.6158</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.4483</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.0536</v>
+        <v>0.6158</v>
       </c>
       <c r="K6" t="n">
-        <v>3.264</v>
+        <v>0.6158</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2103999999999999</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.5284</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.2905</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.2379</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-6.2316</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>6.2315</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4.5039</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.4482</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0558</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4016</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6811</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6158</v>
+        <v>-0.05409999999999993</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6158</v>
+        <v>-1.6708</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.6167</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6158</v>
+        <v>-1.4749</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6158</v>
+        <v>0.9734999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-2.4483</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6158</v>
+        <v>3.0536</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6158</v>
+        <v>3.264</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.2103999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-4.5284</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-2.2905</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-2.2379</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-6.2316</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>6.2315</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.8223</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.2276</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.5948</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.4016</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.6811</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4067</v>
+        <v>-4.5538</v>
       </c>
       <c r="E8" t="n">
-        <v>4.356</v>
+        <v>-2.7735</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.762700000000001</v>
+        <v>-1.7802</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.6366</v>
+        <v>-4.0703</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.9489</v>
+        <v>-1.9421</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6877</v>
+        <v>-2.1282</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8134</v>
+        <v>0.1026999999999996</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.8518</v>
+        <v>1.4221</v>
       </c>
       <c r="L8" t="n">
-        <v>1.0383</v>
+        <v>-1.319299999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.8232</v>
+        <v>-4.1729</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.0971</v>
+        <v>-3.3641</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.7261</v>
+        <v>-0.8088000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7789000000000001</v>
+        <v>1.5579</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.2578</v>
+        <v>-9.9315</v>
       </c>
       <c r="R8" t="n">
-        <v>6.0368</v>
+        <v>11.4895</v>
       </c>
       <c r="S8" t="n">
-        <v>5.2361</v>
+        <v>-1.8309</v>
       </c>
       <c r="T8" t="n">
-        <v>3.7417</v>
+        <v>-0.6239</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4947</v>
+        <v>-1.2071</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.7851</v>
+        <v>-0.2106</v>
       </c>
       <c r="W8" t="n">
-        <v>6.6859</v>
+        <v>7.678900000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>-9.471</v>
+        <v>-7.8896</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.0524</v>
+        <v>-4.6696</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.045</v>
+        <v>-1.0037</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.0074</v>
+        <v>-3.6659</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.0703</v>
+        <v>-1.302200000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9421</v>
+        <v>-1.1795</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1282</v>
+        <v>-0.1226999999999998</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1026999999999996</v>
+        <v>2.4423</v>
       </c>
       <c r="K9" t="n">
-        <v>1.4221</v>
+        <v>-0.5899</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.319299999999999</v>
+        <v>3.0324</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.1729</v>
+        <v>-3.7444</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.3641</v>
+        <v>-0.5892000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8088000000000001</v>
+        <v>-3.1552</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5579</v>
+        <v>-0.7789999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-9.9315</v>
+        <v>-4.089399999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>11.4895</v>
+        <v>3.3104</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.3294</v>
+        <v>-0.8748</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8952</v>
+        <v>-0.526</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.4343</v>
+        <v>-0.3486</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2106</v>
+        <v>-1.7137</v>
       </c>
       <c r="W9" t="n">
-        <v>7.678900000000001</v>
+        <v>1.1695</v>
       </c>
       <c r="X9" t="n">
-        <v>-7.8896</v>
+        <v>-2.8833</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.4595</v>
+        <v>-4.8743</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.588</v>
+        <v>-5.0692</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.8715</v>
+        <v>0.1949999999999998</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.302200000000001</v>
+        <v>-0.8416000000000003</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1795</v>
+        <v>0.4278999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1226999999999998</v>
+        <v>-1.2694</v>
       </c>
       <c r="J10" t="n">
-        <v>2.4423</v>
+        <v>2.8528</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5899</v>
+        <v>2.1632</v>
       </c>
       <c r="L10" t="n">
-        <v>3.0324</v>
+        <v>0.6895</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.7444</v>
+        <v>-3.6941</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5892000000000001</v>
+        <v>-1.7353</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.1552</v>
+        <v>-1.9589</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7789999999999999</v>
+        <v>-3.3107</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.089399999999999</v>
+        <v>-8.178900000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>3.3104</v>
+        <v>4.868300000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.6645</v>
+        <v>-0.6190000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1102</v>
+        <v>-0.8611</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.5543</v>
+        <v>0.242</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.7137</v>
+        <v>-0.1031000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1695</v>
+        <v>1.118</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.8833</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.2506</v>
+        <v>-4.958</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.9526</v>
+        <v>1.3519</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.298</v>
+        <v>-6.31</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8416000000000003</v>
+        <v>-4.6366</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4278999999999999</v>
+        <v>-3.9489</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2694</v>
+        <v>-0.6877</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8528</v>
+        <v>-0.8134</v>
       </c>
       <c r="K11" t="n">
-        <v>2.1632</v>
+        <v>-1.8518</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6895</v>
+        <v>1.0383</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.6941</v>
+        <v>-3.8232</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7353</v>
+        <v>-2.0971</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.9589</v>
+        <v>-1.7261</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.3107</v>
+        <v>0.7789000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-8.178900000000001</v>
+        <v>-5.2578</v>
       </c>
       <c r="R11" t="n">
-        <v>4.868300000000001</v>
+        <v>6.0368</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.9953</v>
+        <v>1.6847</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.7442</v>
+        <v>0.7373999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.2509</v>
+        <v>0.9473</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1031000000000001</v>
+        <v>-2.7851</v>
       </c>
       <c r="W11" t="n">
-        <v>1.118</v>
+        <v>6.6859</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2211</v>
+        <v>-9.471</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.164400000000001</v>
+        <v>-7.4952</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4471</v>
+        <v>-0.4642000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.7171</v>
+        <v>-7.031000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>0.1027</v>
@@ -1390,13 +1390,13 @@
         <v>5.258</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.4415</v>
+        <v>-0.7724</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.8772</v>
+        <v>-0.8943</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5643</v>
+        <v>0.1217</v>
       </c>
       <c r="V12" t="n">
         <v>-4.8782</v>
@@ -1423,34 +1423,34 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>6.559799999999994</v>
+        <v>15.0143</v>
       </c>
       <c r="E13" t="n">
-        <v>24.4756</v>
+        <v>26.9495</v>
       </c>
       <c r="F13" t="n">
-        <v>-17.9151</v>
+        <v>-11.9349</v>
       </c>
       <c r="G13" t="n">
-        <v>17.2767</v>
+        <v>17.27670000000001</v>
       </c>
       <c r="H13" t="n">
         <v>16.8418</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4351000000000004</v>
+        <v>0.4351000000000006</v>
       </c>
       <c r="J13" t="n">
-        <v>57.40910000000001</v>
+        <v>57.4091</v>
       </c>
       <c r="K13" t="n">
-        <v>41.67460000000001</v>
+        <v>41.67460000000002</v>
       </c>
       <c r="L13" t="n">
         <v>15.7347</v>
       </c>
       <c r="M13" t="n">
-        <v>-40.1316</v>
+        <v>-40.13159999999999</v>
       </c>
       <c r="N13" t="n">
         <v>-24.8325</v>
@@ -1468,13 +1468,13 @@
         <v>81.78930000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-14.836</v>
+        <v>-6.3821</v>
       </c>
       <c r="T13" t="n">
-        <v>-10.2759</v>
+        <v>-7.8026</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.5595</v>
+        <v>1.4206</v>
       </c>
       <c r="V13" t="n">
         <v>-6.5908</v>
